--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26307,7 +26307,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27875,7 +27875,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31011,7 +31011,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32579,7 +32579,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34837,7 +34837,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36707,7 +36707,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40677,7 +40677,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42777,7 +42777,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46977,7 +46977,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -49077,7 +49077,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51177,7 +51177,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53277,7 +53277,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55377,7 +55377,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57477,7 +57477,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">

--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20035,7 +20035,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26307,7 +26307,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27875,7 +27875,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31011,7 +31011,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32579,7 +32579,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34837,7 +34837,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36707,7 +36707,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40677,7 +40677,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42777,7 +42777,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46977,7 +46977,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -49077,7 +49077,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51177,7 +51177,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53277,7 +53277,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55377,7 +55377,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57477,7 +57477,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">

--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5679,9 +5679,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5933,7 +5930,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6463,9 +6460,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6717,7 +6711,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7247,9 +7241,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7501,7 +7492,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8031,9 +8022,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8285,7 +8273,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8815,9 +8803,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9069,7 +9054,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9599,9 +9584,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9853,7 +9835,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10383,9 +10365,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10637,7 +10616,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11167,9 +11146,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -11421,7 +11397,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11951,9 +11927,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12205,7 +12178,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12735,9 +12708,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12989,7 +12959,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13519,9 +13489,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13773,7 +13740,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14303,9 +14270,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14557,7 +14521,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15087,9 +15051,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15341,7 +15302,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15871,9 +15832,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -16125,7 +16083,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16655,9 +16613,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16909,7 +16864,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17439,9 +17394,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -17693,7 +17645,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18223,9 +18175,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -18477,7 +18426,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19007,9 +18956,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -19261,7 +19207,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19791,9 +19737,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -20045,7 +19988,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20575,9 +20518,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -20829,7 +20769,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21359,9 +21299,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -21613,7 +21550,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22143,9 +22080,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -22397,7 +22331,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22927,9 +22861,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -23181,7 +23112,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23711,9 +23642,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -23965,7 +23893,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24495,9 +24423,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -24749,7 +24674,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25279,9 +25204,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -25533,7 +25455,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26063,9 +25985,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -26317,7 +26236,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26847,9 +26766,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -27101,7 +27017,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27631,9 +27547,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -27885,7 +27798,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28415,9 +28328,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -28669,7 +28579,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29199,9 +29109,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -29453,7 +29360,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29983,9 +29890,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -30237,7 +30141,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30767,9 +30671,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -31021,7 +30922,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31551,9 +31452,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -31805,7 +31703,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32335,9 +32233,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -32589,7 +32484,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33119,9 +33014,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -33373,7 +33265,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33990,7 +33882,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -34220,7 +34112,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34593,9 +34485,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -34847,7 +34736,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -34999,9 +34888,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -35860,7 +35746,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36090,7 +35976,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36463,9 +36349,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -36717,7 +36600,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36869,9 +36752,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -37730,7 +37610,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -37960,7 +37840,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38333,9 +38213,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -38587,7 +38464,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -38739,9 +38616,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -39600,7 +39474,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39830,7 +39704,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -40433,9 +40307,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -40687,7 +40558,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40839,9 +40710,6 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -41700,7 +41568,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41930,7 +41798,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -42533,9 +42401,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -42787,7 +42652,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42939,9 +42804,6 @@
       <c r="O215" t="n">
         <v>8</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.1656787210016936</v>
       </c>
@@ -43800,7 +43662,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44030,7 +43892,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -44633,9 +44495,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -44887,7 +44746,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -45039,9 +44898,6 @@
       <c r="O225" t="n">
         <v>38</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.7869739247580443</v>
       </c>
@@ -45900,7 +45756,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46130,7 +45986,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -46733,9 +46589,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -46987,7 +46840,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -47139,9 +46992,6 @@
       <c r="O235" t="n">
         <v>744</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>15.4081210531575</v>
       </c>
@@ -48000,7 +47850,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48230,7 +48080,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -48833,9 +48683,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -49087,7 +48934,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -49239,9 +49086,6 @@
       <c r="O245" t="n">
         <v>418</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>8.656713172338488</v>
       </c>
@@ -50100,7 +49944,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -50330,7 +50174,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -50933,9 +50777,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -51187,7 +51028,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -51339,9 +51180,6 @@
       <c r="O255" t="n">
         <v>403</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>8.346065570460313</v>
       </c>
@@ -52200,7 +52038,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52430,7 +52268,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -53033,9 +52871,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -53287,7 +53122,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -53439,9 +53274,6 @@
       <c r="O265" t="n">
         <v>4802</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>99.44865228126655</v>
       </c>
@@ -54300,7 +54132,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54530,7 +54362,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -55133,9 +54965,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -55387,7 +55216,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -55539,9 +55368,6 @@
       <c r="O275" t="n">
         <v>5763</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>119.350808641595</v>
       </c>
@@ -56400,7 +56226,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -56630,7 +56456,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -57233,9 +57059,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -57487,7 +57310,7 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN284" t="b">
@@ -57638,9 +57461,6 @@
       </c>
       <c r="O285" t="n">
         <v>278</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
       </c>
       <c r="R285" t="n">
         <v>5.757335554808851</v>

--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31693,7 +31693,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34726,7 +34726,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42642,7 +42642,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46830,7 +46830,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51018,7 +51018,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53112,7 +53112,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55206,7 +55206,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">

--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31693,7 +31693,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34726,7 +34726,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42642,7 +42642,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46830,7 +46830,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51018,7 +51018,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53112,7 +53112,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55206,7 +55206,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">

--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31693,7 +31693,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34726,7 +34726,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42642,7 +42642,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46830,7 +46830,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51018,7 +51018,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53112,7 +53112,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55206,7 +55206,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">

--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31693,7 +31693,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34726,7 +34726,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42642,7 +42642,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46830,7 +46830,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51018,7 +51018,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53112,7 +53112,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55206,7 +55206,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
